--- a/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
+++ b/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
@@ -573,7 +573,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>494472.34</v>
+        <v>500977.05</v>
       </c>
     </row>
     <row r="3">
@@ -638,7 +638,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5669438.88</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="4">
@@ -699,7 +699,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>65094.36</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="5">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1035505.11</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="6">
@@ -825,7 +825,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>696818.85</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="7">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5386172.79</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="8">
@@ -955,7 +955,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>727892.1</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="9">
@@ -1020,7 +1020,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>799431.89</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="10">
@@ -1085,7 +1085,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1095642.44</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="11">
@@ -1150,7 +1150,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>577504.36</v>
+        <v>581414.84</v>
       </c>
     </row>
     <row r="12">
@@ -1215,7 +1215,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>1406029.91</v>
+        <v>1399224.97</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
+++ b/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>598002-22-SE25</t>
+          <t>544143-1-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,32 +524,32 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-01-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.810.001-6</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Servicio de Bienestar del Personal de la SVS</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -562,24 +562,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>500977.05</v>
+        <v>30183.07</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>425-1046-SE25</t>
+          <t>544143-2-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -589,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -604,17 +600,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -627,24 +623,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>5708070.46</v>
+        <v>31876.29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>544143-3-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-03-25</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -669,17 +661,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -699,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>63593.52</v>
+        <v>33074.59</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>544143-6-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -715,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-05-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -730,17 +722,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Bienestar</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -760,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1064847.91</v>
+        <v>32668.39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>544143-7-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -776,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -791,17 +783,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -814,24 +806,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>716564.4</v>
+        <v>33001.67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>593951-78-SE26</t>
+          <t>2667-315-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -841,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -856,17 +844,17 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Región Metropolitana de Santiago</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -879,24 +867,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5472729.65</v>
+        <v>319155.93</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>544143-9-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -906,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2025-07-03</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -921,17 +905,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -944,24 +928,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>32929.75</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>544143-10-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -971,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2025-07-30</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -986,17 +966,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1009,24 +989,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>31494.61</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>544143-11-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1036,12 +1012,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2025-09-01</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1051,12 +1027,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>60.701.002-1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1074,24 +1050,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>1086862.81</v>
+        <v>31703.34</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>545927-3-SE26</t>
+          <t>5212-13-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1101,12 +1073,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1116,17 +1088,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.212.000-5</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE TRANSPORTES</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t xml:space="preserve">Región de Valparaíso </t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1150,72 +1122,1377 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>581414.84</v>
+        <v>923764.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
+          <t>544143-12-CM25</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>31911.74</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>544143-13-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>oct-2025</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2025-10-30</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>32699.85</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>544143-14-CM25</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2025-12-11</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>33211.71</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>544143-15-CM25</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2025-12-26</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>33998.64</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>425-1046-SE25</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>dic-2025</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2025-12-31</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>60.301.001-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>5708070.46</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>574800-1-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ene-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-01-06</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>60.601.000-1</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Subsecretaria de Relaciones Exteriores</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>63593.52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>544143-1-CM26</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>2026-02-17</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>38186.96</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>544143-2-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>37884.62</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>575437-3-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>60.805.312-3</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Bienestar</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>1064847.91</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>574800-3-SE26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-03-03</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>60.601.000-1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Subsecretaria de Relaciones Exteriores</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>716564.4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>593951-78-SE26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>2026-03-05</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>70.574.900-0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>5472729.65</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>1149280-4-SE26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-03-27</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>60.400.000-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>717480.3100000001</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>544143-4-CM26</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>35854.46</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>544143-5-CM26</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2026-05-08</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>37633.13</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2667-214-CM26</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>2026-05-15</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>69.255.600-3</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>361779.55</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>544143-6-CM26</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>38298.12</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1515286-3-SE26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-06-05</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>53.337.014-4</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>805575.1800000001</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>5212-57-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>60.921.000-1</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Tarapacá  </t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>1086862.81</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>544143-7-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>37065.48</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
           <t>1211839-502-SE26</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D31" t="inlineStr">
         <is>
           <t>2026-07-30</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
         <is>
           <t>70.856.400-1</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Metropolitana</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
         <is>
           <t xml:space="preserve">Región de Tarapacá  </t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="n">
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
         <v>1399224.97</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>544143-8-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-07-31</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>37139.79</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>544143-9-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>60.701.002-1</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>SERV NACIONAL DE PESCA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Región de Valparaíso </t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>37448.52</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
+++ b/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="seguro-colectivo top org" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="seguro-colectivo top org" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1113,7 +1113,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1163,7 +1163,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1422,7 +1422,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1731,7 +1731,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -1796,7 +1796,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2472,7 +2472,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">

--- a/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
+++ b/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>544143-1-CM25</t>
+          <t>1477-30-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-01-28</t>
+          <t>2025-01-29</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,17 +539,17 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>30183.07</v>
+        <v>27717.33</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>544143-2-CM25</t>
+          <t>1477-76-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>feb-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,17 +600,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>31876.29</v>
+        <v>29292.08</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>544143-3-CM25</t>
+          <t>1477-116-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-25</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,17 +661,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>33074.59</v>
+        <v>30453.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>544143-6-CM25</t>
+          <t>1477-153-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-05-08</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,17 +722,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>32668.39</v>
+        <v>30864.75</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>544143-7-CM25</t>
+          <t>1477-187-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -783,17 +783,17 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>33001.67</v>
+        <v>30885.16</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2667-315-CM25</t>
+          <t>1477-220-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-17</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>319155.93</v>
+        <v>31182.23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>544143-9-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-07-03</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,17 +905,17 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>32929.75</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>544143-10-CM25</t>
+          <t>1477-281-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +951,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-07-30</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,17 +966,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>31494.61</v>
+        <v>30252.99</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>544143-11-CM25</t>
+          <t>1477-304-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-09-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1027,17 +1027,17 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1057,7 +1057,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>31703.34</v>
+        <v>31178.91</v>
       </c>
     </row>
     <row r="11">
@@ -1128,7 +1128,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>544143-12-CM25</t>
+          <t>1477-345-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-10-01</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,17 +1153,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1183,13 +1183,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31911.74</v>
+        <v>31591.68</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>544143-13-CM25</t>
+          <t>1477-369-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1199,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-10-30</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1214,17 +1214,17 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1244,13 +1244,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32699.85</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>544143-14-CM25</t>
+          <t>1477-416-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1275,17 +1275,17 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1305,13 +1305,13 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>33211.71</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>544143-15-CM25</t>
+          <t>425-1046-SE25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-26</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,17 +1336,17 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1359,20 +1359,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>33998.64</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>425-1046-SE25</t>
+          <t>574800-1-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1382,12 +1386,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1397,12 +1401,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1420,24 +1424,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>5708070.46</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>63593.52</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>544143-1-CM26</t>
+          <t>1477-47-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1523,17 +1523,17 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1553,13 +1553,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>38186.96</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>544143-2-CM26</t>
+          <t>575437-3-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1574,7 +1574,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,17 +1584,17 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>60.805.312-3</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1614,13 +1614,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>37884.62</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>574800-3-SE26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1645,12 +1645,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bienestar</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1668,20 +1668,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1064847.91</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>593951-78-SE26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1696,7 +1700,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1706,12 +1710,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Subsecretaria de Relaciones Exteriores</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1740,13 +1744,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>716564.4</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>593951-78-SE26</t>
+          <t>1149280-4-SE26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1761,7 +1765,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1771,12 +1775,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1805,13 +1809,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5472729.65</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>1477-81-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1826,7 +1830,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1836,12 +1840,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1859,24 +1863,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>35281.5</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>544143-4-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-01</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1924,20 +1924,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>35854.46</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>544143-5-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1947,12 +1951,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-05-08</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1962,17 +1966,17 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1992,13 +1996,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>37633.13</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2667-214-CM26</t>
+          <t>1477-163-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2008,12 +2012,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-05-15</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2023,12 +2027,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2053,13 +2057,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>361779.55</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>544143-6-CM26</t>
+          <t>1515286-3-SE26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2074,27 +2078,27 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>53.337.014-4</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2107,20 +2111,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr"/>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L27" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>38298.12</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>5212-57-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2135,7 +2143,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -2145,17 +2153,17 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fondo de Bienestar de la Corporación de Fomento </t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2179,13 +2187,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2200,7 +2208,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2210,17 +2218,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2233,24 +2241,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>1086862.81</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>544143-7-CM26</t>
+          <t>1211839-502-SE26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2265,7 +2269,7 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2275,17 +2279,17 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2298,20 +2302,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L30" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>37065.48</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1211839-502-SE26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2326,7 +2334,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2336,12 +2344,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2359,24 +2367,20 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>Tarapacá</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>1399224.97</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>544143-8-CM26</t>
+          <t>1477-270-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2386,12 +2390,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2401,17 +2405,17 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2431,13 +2435,13 @@
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37139.79</v>
+        <v>37103.35</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>544143-9-CM26</t>
+          <t>1477-295-CM26</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2447,12 +2451,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>sep-2026</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -2462,17 +2466,17 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>60.701.002-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>SERV NACIONAL DE PESCA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2492,7 +2496,7 @@
         </is>
       </c>
       <c r="M33" s="2" t="n">
-        <v>37448.52</v>
+        <v>35397.27</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
+++ b/docs/oc-top-organismos/seguro-colectivo-de-vida-con-adicional-de-salud.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M33"/>
+  <dimension ref="A1:M34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -575,7 +579,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1477-76-CM25</t>
+          <t>593951-35-SE25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,27 +589,27 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>mar-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-03-03</t>
+          <t>2025-02-06</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -623,20 +627,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29292.08</v>
+        <v>4811254.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1477-116-CM25</t>
+          <t>1477-76-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +659,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-03-24</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -684,20 +692,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>30453.26</v>
+        <v>29292.08</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1477-153-CM25</t>
+          <t>1477-116-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +719,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>abr-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-04-29</t>
+          <t>2025-03-24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -745,20 +757,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>30864.75</v>
+        <v>30453.26</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1477-187-CM25</t>
+          <t>1477-153-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +784,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>may-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-05-27</t>
+          <t>2025-04-29</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -806,20 +822,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>30885.16</v>
+        <v>30864.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1477-220-CM25</t>
+          <t>1477-187-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +849,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-05-27</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -867,20 +887,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>31182.23</v>
+        <v>30885.16</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1477-247-CM25</t>
+          <t>1477-220-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +914,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>jul-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-07-24</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -928,20 +952,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>30775.84</v>
+        <v>31182.23</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1477-281-CM25</t>
+          <t>1477-247-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -951,12 +979,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ago-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-07-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -989,20 +1017,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>30252.99</v>
+        <v>30775.84</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1477-304-CM25</t>
+          <t>1477-281-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,12 +1044,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>sep-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1050,20 +1082,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>31178.91</v>
+        <v>30252.99</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>5212-13-CM25</t>
+          <t>1477-304-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1078,7 +1114,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2025-09-30</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,17 +1124,17 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1122,13 +1158,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>923764.08</v>
+        <v>31178.91</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1477-345-CM25</t>
+          <t>5212-13-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1174,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>oct-2025</t>
+          <t>sep-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2025-10-24</t>
+          <t>2025-09-30</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,17 +1189,17 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1176,20 +1212,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>31591.68</v>
+        <v>923764.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1477-369-CM25</t>
+          <t>1477-345-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1199,12 +1239,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-10-24</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1237,20 +1277,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>32019.45</v>
+        <v>31591.68</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1477-416-CM25</t>
+          <t>1477-369-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1260,12 +1304,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025-12-19</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1298,20 +1342,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>32738.51</v>
+        <v>32019.45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>425-1046-SE25</t>
+          <t>1477-416-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1326,7 +1374,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2025-12-19</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1336,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>60.301.001-9</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1370,13 +1418,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5708070.46</v>
+        <v>32738.51</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>574800-1-CM26</t>
+          <t>425-1046-SE25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,12 +1434,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-01-06</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.301.001-9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>CORP ADMINISTRATIVA DEL PODER JUDICIAL</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1424,20 +1472,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>63593.52</v>
+        <v>5708070.46</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1477-24-CM26</t>
+          <t>574800-1-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1452,7 +1504,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1462,12 +1514,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1485,20 +1537,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>37905.05</v>
+        <v>63593.52</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1477-47-CM26</t>
+          <t>1477-24-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,12 +1564,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1546,20 +1602,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>37714.34</v>
+        <v>37905.05</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>575437-3-CM26</t>
+          <t>1477-47-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1569,12 +1629,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-03-03</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,12 +1644,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>60.805.312-3</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1607,20 +1667,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>1064847.91</v>
+        <v>37714.34</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>574800-3-SE26</t>
+          <t>575437-3-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1645,12 +1709,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>60.601.000-1</t>
+          <t>60.805.312-3</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
+          <t>TESORERIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1679,13 +1743,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>716564.4</v>
+        <v>1064847.91</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>593951-78-SE26</t>
+          <t>574800-3-SE26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1700,7 +1764,7 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-03-05</t>
+          <t>2026-03-03</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1710,12 +1774,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>70.574.900-0</t>
+          <t>60.601.000-1</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
+          <t>SUBSECRETARIA DE RELACIONES EXTERIORES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1744,13 +1808,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>5472729.65</v>
+        <v>716564.4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>1149280-4-SE26</t>
+          <t>593951-78-SE26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1765,7 +1829,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-03-27</t>
+          <t>2026-03-05</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1775,12 +1839,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>60.400.000-9</t>
+          <t>70.574.900-0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
+          <t>FUNDACION EDUCACIONAL PARA EL DESAROLLO INTEGRAL DE LA NIÑEZ</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1809,13 +1873,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>717480.3100000001</v>
+        <v>5472729.65</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1477-81-CM26</t>
+          <t>1149280-4-SE26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1830,7 +1894,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-03-31</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1840,12 +1904,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.400.000-9</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CONTRALORIA GENERAL DE LA REPUBLICA</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1863,20 +1927,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>35281.5</v>
+        <v>717480.3100000001</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>4973-40-SE26</t>
+          <t>1477-81-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1886,12 +1954,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1901,12 +1969,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.202.016-7</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1935,13 +2003,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1573308.56</v>
+        <v>35281.5</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1477-108-CM26</t>
+          <t>4973-40-SE26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1956,7 +2024,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1966,12 +2034,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>61.202.016-7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1989,20 +2057,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>36973.69</v>
+        <v>1573308.56</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1477-163-CM26</t>
+          <t>1477-108-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2012,12 +2084,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -2050,20 +2122,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>37700.6</v>
+        <v>36973.69</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1515286-3-SE26</t>
+          <t>1477-163-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2078,22 +2154,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-06-05</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>53.337.014-4</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2122,13 +2198,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>805575.1800000001</v>
+        <v>37700.6</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>5212-57-CM26</t>
+          <t>1515286-3-SE26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2143,27 +2219,27 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-06-08</t>
+          <t>2026-06-05</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.921.000-1</t>
+          <t>53.337.014-4</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE VALPARAISO</t>
+          <t>CORPORACION DE FOMENTO DE LA PRODUCCION</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2187,13 +2263,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>1086862.81</v>
+        <v>805575.1800000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1477-194-CM26</t>
+          <t>5212-57-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2208,7 +2284,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-08</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2218,17 +2294,17 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>60.921.000-1</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>UNIVERSIDAD DE VALPARAISO</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2241,20 +2317,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M29" s="2" t="n">
-        <v>36957.96</v>
+        <v>1086862.81</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>1211839-502-SE26</t>
+          <t>1477-194-CM26</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2264,12 +2344,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -2279,12 +2359,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>70.856.400-1</t>
+          <t>70.786.200-9</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
+          <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -2313,13 +2393,13 @@
         </is>
       </c>
       <c r="M30" s="2" t="n">
-        <v>1399224.97</v>
+        <v>36957.96</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>1477-242-CM26</t>
+          <t>1211839-502-SE26</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2334,7 +2414,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -2344,12 +2424,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>70.786.200-9</t>
+          <t>70.856.400-1</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Corporación de Asistencia Judicial RM</t>
+          <t>CORP MUNIC EDUC SALUD Y ATENCION</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -2367,20 +2447,24 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr"/>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L31" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M31" s="2" t="n">
-        <v>36580.68</v>
+        <v>1399224.97</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>1477-270-CM26</t>
+          <t>1477-242-CM26</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2390,12 +2474,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -2428,74 +2512,147 @@
           <t>96.573.600-K</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M32" s="2" t="n">
-        <v>37103.35</v>
+        <v>36580.68</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>1477-270-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>70.786.200-9</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Corporación de Asistencia Judicial RM</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>37103.35</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>1477-295-CM26</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2239-12-LR23</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-12-LR23</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D33" t="inlineStr">
+      <c r="D34" t="inlineStr">
         <is>
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Aceptada</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
         <is>
           <t>70.786.200-9</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>Corporación de Asistencia Judicial RM</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>BCI SEGUROS VIDA S A</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>96.573.600-K</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="n">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>BCI SEGUROS VIDA S A</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>96.573.600-K</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>Tarapacá</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
         <v>35397.27</v>
       </c>
     </row>
